--- a/CookingClient/Assets/_Project/Data/Tables/NightTables.xlsx
+++ b/CookingClient/Assets/_Project/Data/Tables/NightTables.xlsx
@@ -969,35 +969,852 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>e</t>
+          <t>eventId</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>optionId</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>phase</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>order</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>text</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>o</t>
+          <t>event_mushroom</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Intro</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>行走时，你的脚尖似乎踢到了什么柔软的东西。借着微弱的光亮查看，原来是蘑菇的菌盖。出乎意料的是，它的根须似乎深深扎入了泥土，不愿轻易离开。</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>p</t>
+          <t>event_mushroom</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>opt_mushroom_pull</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>你手脚并用，紧紧环住蘑菇，仿佛在使用一种针对菌类的柔术。泥土的颗粒卡进了你的指甲缝，随后噗通一声，你和蘑菇一起躺倒在地。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>o</t>
+          <t>event_mushroom</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>opt_mushroom_pull</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>蘑菇与地面之间难道只有真空吗？你无法与这股巨大的吸力抗衡，摇摇头遗憾离场。只是可惜了你好不容易洗干净的裤子，这会膝盖上都是泥巴。</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>t</t>
+          <t>event_mushroom</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>opt_mushroom_pinch</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>长长的指甲终于有了用武之地，你用指尖确认着触感剖开伞盖。你成功割下一轮蘑菇的清香作为今夜的收获。蘑菇柄留在原地，像新伐的树桩。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>event_mushroom</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>opt_mushroom_pinch</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>event_merchant</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Intro</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>这个商人不声不响从阴影里出现，把你吓了一跳。“我这有好交易！”他诱惑地嘶嘶道。你盯着那双蛇般的眼眸，意识到自己要做出选择。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>event_merchant</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>opt_merchant_trade</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>“好孩子……”商人喃喃自语地抚摸着你交给他的货物，这诡异的一幕叫人不寒而栗。他一副急于打发走你的样子，硬是塞给你一袋沉甸甸的肉块。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>event_merchant</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>opt_merchant_trade</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>商人给了你一些金币。不过钱真的有用吗？仿佛要印证你的想法，金币们在目光中化成粉末，随风飘散了。你意识到自己的受骗，然而加害者早已走远。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>event_merchant</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>opt_merchant_leave</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>你不太乐意和他做交易，商人也没多说什么。比起人类，你更愿意相信大地的恩赐——播种带来收获。你埋下谷物，然后掘起地下丰收的果实。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>event_merchant</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>opt_merchant_leave</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>event_beasts</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Intro</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>一对，也就是两只钢背兽夫妇为幼崽的抚养方针、房贷和家务分配起了冲突。它们朝彼此低吼，鳞片碰撞摩擦出火花，在黑暗中明明灭灭。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>event_beasts</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>opt_beasts_mediate</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>你利用自己灵巧的手指，帮它们解开了麻烦源之一——洞穴深处纠结的藤蔓。钢背兽们感谢了你，然后迅速陷入了下一轮争吵，接着演变为斗殴。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>event_beasts</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>opt_beasts_mediate</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>凡人不应该插手此类战斗！你确信自己失去了不小心被波及的记忆片段，这是你的大脑在保护你，大概。你的下腹火辣辣地疼痛，肋骨也断了几根。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>event_beasts</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>opt_beasts_watch</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>世界上唯一比钢背兽的头骨更坚硬的是另一只钢背兽的头骨。谁也不服输的痛殴让它们双双晕倒在地，脑门隆起鸡蛋大的肿包。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>event_beasts</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>opt_beasts_watch</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>event_beasts</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>opt_beasts_side</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>你坚定地选择了其中一边押宝。收到你加油助威的钢背兽备受鼓舞，一口气掀翻了对方，得意洋洋地看着配偶四脚朝天扭动着，试图翻身再战。</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>event_beasts</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>opt_beasts_side</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>这回你可赌错了。你最不希望看见的胜者仰头长啸，目露凶光地转向你。不用说，你为了小命飞一般地逃离了现场，连要摔一跤都忘了。</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>event_fishing</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Intro</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>月色下，芦苇丛，影子轻轻晃动，清池起涟漪。你祈祷这阵微风不会吓走你的鱼儿。突然！线绷直了，巨力从弯鱼竿的那头传来。大的要来了！</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>event_fishing</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>opt_fishing_cast</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>你直起腰奋力，试图将大鱼拉离水面，浑身的肌肉好像也要跟着拉断。但这一切都是值得的，瞧瞧那金黄的鳞片吧，底下一定卧着鲜美的鱼肉。</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>event_fishing</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>opt_fishing_cast</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>鱼不费吹灰之力就扯断了线，还挑衅似的跳出水面，顺便扬起尾巴拍了你一脸浪花。你抖落水珠，拧干衣服，发誓一定要报这仇。</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>event_fishing</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>opt_fishing_wait</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>你沉住气，拉开架势与鱼周旋。它的体力终究是有限的，在世纪般漫长的博弈后，你和鱼达成了某种宿敌式的友谊。安息吧，挚友，我会好好把你安葬在腹中。</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>event_fishing</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>opt_fishing_wait</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>event_grave</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Intro</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>1</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>静静的碑石是冰冷的，死去的人们永眠于此。</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>event_grave</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>opt_grave_mourn</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>1</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>一股冷意掠过了后脖子，你下意识地耸肩回头，原来只是风从植物的缝隙中吹过来。</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>event_grave</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>opt_grave_mourn</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>2</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>……不过它们原本就在这里吗？</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>event_grave</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>opt_grave_mourn</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>event_grave</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>opt_grave_flower</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>1</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>你把瘦弱的花圈加冕于墓碑。摘花时，一些形状特殊的草叶引起了你的注意。你窸窸窣窣地拨开它们，一只小鼠仓皇逃窜，把自己的库存拱手相让。</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>event_grave</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>opt_grave_flower</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>1</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>event_moonstone</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Intro</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>1</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>石头在月光下有着摄人心魄的美，那抹白色浓得近乎于鲜血。也许它本就是月岩的一部分，所以才如此圣洁。你发觉自己的双脚正朝它迈动。</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>event_moonstone</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>opt_moon_look</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>石头边，一滩水倒映着月亮。水洼正急剧缩小，你意识到这是那块石头在吸水。石头的颜色显得越发丰盈了，而水中的小鱼小虾纷纷在干渴中蹦起来。</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>event_moonstone</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>opt_moon_look</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>1</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>event_moonstone</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>opt_moon_touch</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>1</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>你把自己的双手按在石头的表面上，它比你想的还要光滑。随着手部的动作，脑海中竟也响起音乐声。你飘飘欲仙，感到自己无所不能，可以创造一切，甚至一根黄瓜。</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>event_moonstone</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>opt_moon_touch</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>1</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
